--- a/results_Uncertain_parameters_and_OF_values/melhores_simulacoes_por_grupo.xlsx
+++ b/results_Uncertain_parameters_and_OF_values/melhores_simulacoes_por_grupo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,7 +527,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -607,7 +607,7 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -647,47 +647,7 @@
         <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Sim158</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.6148546382980264</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.7210108900395958</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.834443993337176</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.7332350698650159</v>
-      </c>
-      <c r="I6" t="n">
-        <v>20.79356906554032</v>
-      </c>
-      <c r="J6" t="n">
-        <v>158</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
